--- a/data/trans_orig/P36BPD12_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD12_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que consumen frutos secos a la semana en 2023</t>
+          <t>Población según el número de veces que consumen frutos secos a la semana en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>120593</t>
+          <t>120298</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>164245</t>
+          <t>161575</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>224245</t>
+          <t>223763</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>263263</t>
+          <t>263473</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>354675</t>
+          <t>354177</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>414158</t>
+          <t>412979</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>268174</t>
+          <t>267586</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>325409</t>
+          <t>323393</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278106</t>
+          <t>277459</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>319148</t>
+          <t>319437</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>562112</t>
+          <t>558583</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>627868</t>
+          <t>628261</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,22%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>167203</t>
+          <t>170996</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>228212</t>
+          <t>233004</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>114719</t>
+          <t>113516</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>148299</t>
+          <t>146555</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>293993</t>
+          <t>291628</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>365270</t>
+          <t>362657</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>153312</t>
+          <t>135082</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>366286</t>
+          <t>368532</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>306772</t>
+          <t>304147</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>354833</t>
+          <t>355900</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>407593</t>
+          <t>414306</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>705230</t>
+          <t>707310</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>567765</t>
+          <t>564895</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>931018</t>
+          <t>953231</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>444187</t>
+          <t>442952</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>497904</t>
+          <t>495912</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1042527</t>
+          <t>1042747</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1502246</t>
+          <t>1499298</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,7%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>116640</t>
+          <t>103667</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>268930</t>
+          <t>269986</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>137965</t>
+          <t>137403</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>180086</t>
+          <t>178005</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>240055</t>
+          <t>235878</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>416487</t>
+          <t>418493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>227809</t>
+          <t>227855</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>287889</t>
+          <t>287752</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>143813</t>
+          <t>124816</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>342946</t>
+          <t>346592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>334140</t>
+          <t>303921</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>610445</t>
+          <t>602977</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>283386</t>
+          <t>281152</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>342733</t>
+          <t>344950</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>354430</t>
+          <t>352971</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>681758</t>
+          <t>722657</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>664648</t>
+          <t>669473</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1077841</t>
+          <t>1116088</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113930</t>
+          <t>113642</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163717</t>
+          <t>163084</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90718</t>
+          <t>88851</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>259695</t>
+          <t>259395</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>209972</t>
+          <t>208431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>395339</t>
+          <t>398340</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>355619</t>
+          <t>356676</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>425073</t>
+          <t>420673</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>362773</t>
+          <t>373975</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>496364</t>
+          <t>497149</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>746649</t>
+          <t>733267</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>898365</t>
+          <t>895299</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,33%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>348593</t>
+          <t>352289</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>415008</t>
+          <t>418962</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>297319</t>
+          <t>299728</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>410313</t>
+          <t>410518</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>666845</t>
+          <t>671240</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>804980</t>
+          <t>803798</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>132465</t>
+          <t>133038</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>179980</t>
+          <t>186150</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202668</t>
+          <t>201315</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>424547</t>
+          <t>430351</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>352790</t>
+          <t>355405</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>607944</t>
+          <t>622690</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>842879</t>
+          <t>819866</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1170384</t>
+          <t>1169226</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1012179</t>
+          <t>1033252</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1388886</t>
+          <t>1388564</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2040403</t>
+          <t>2067202</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2524077</t>
+          <t>2531120</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1542506</t>
+          <t>1545399</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2070194</t>
+          <t>2122918</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1481323</t>
+          <t>1494700</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2010684</t>
+          <t>2023782</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3083933</t>
+          <t>3069504</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3845222</t>
+          <t>3828642</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,85%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>548334</t>
+          <t>510350</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>769799</t>
+          <t>766420</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>613826</t>
+          <t>616878</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>912251</t>
+          <t>920378</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1251466</t>
+          <t>1249143</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1617410</t>
+          <t>1631000</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD12_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD12_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>139118</t>
+          <t>155664</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>120298</t>
+          <t>134164</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161575</t>
+          <t>180880</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>243509</t>
+          <t>259660</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>223763</t>
+          <t>236773</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>263473</t>
+          <t>279633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>382627</t>
+          <t>415324</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>354177</t>
+          <t>387343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>412979</t>
+          <t>449981</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,79%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>295975</t>
+          <t>319321</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>267586</t>
+          <t>291769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>323393</t>
+          <t>349345</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>297921</t>
+          <t>322368</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>277459</t>
+          <t>301329</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>319437</t>
+          <t>345050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>593895</t>
+          <t>641688</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>558583</t>
+          <t>607651</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>628261</t>
+          <t>677078</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,83%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>196436</t>
+          <t>211808</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>170996</t>
+          <t>185140</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>233004</t>
+          <t>244325</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>130057</t>
+          <t>146742</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>113516</t>
+          <t>128167</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>146555</t>
+          <t>166977</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>326493</t>
+          <t>358549</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>291628</t>
+          <t>326978</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>362657</t>
+          <t>392663</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>631529</t>
+          <t>686792</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>631529</t>
+          <t>686792</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>631529</t>
+          <t>686792</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>671487</t>
+          <t>728770</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>671487</t>
+          <t>728770</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>671487</t>
+          <t>728770</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1303015</t>
+          <t>1415561</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1303015</t>
+          <t>1415561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1303015</t>
+          <t>1415561</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>282338</t>
+          <t>295394</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>135082</t>
+          <t>265081</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368532</t>
+          <t>331118</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>330499</t>
+          <t>366930</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>304147</t>
+          <t>340355</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>355900</t>
+          <t>399040</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>612838</t>
+          <t>662325</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>414306</t>
+          <t>623266</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>707310</t>
+          <t>706734</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>707787</t>
+          <t>514136</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>564895</t>
+          <t>475323</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>953231</t>
+          <t>550856</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>471416</t>
+          <t>528978</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>442952</t>
+          <t>497473</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>495912</t>
+          <t>557742</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1179204</t>
+          <t>1043114</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1042747</t>
+          <t>996054</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1499298</t>
+          <t>1090808</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>51,46%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>202738</t>
+          <t>239387</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103667</t>
+          <t>207948</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>269986</t>
+          <t>272684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,27 +1442,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>156191</t>
+          <t>174930</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>137403</t>
+          <t>154195</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>178005</t>
+          <t>198919</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>358930</t>
+          <t>414317</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>235878</t>
+          <t>375202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>418493</t>
+          <t>452829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>256656</t>
+          <t>295239</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>227855</t>
+          <t>264320</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>287752</t>
+          <t>329908</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>259350</t>
+          <t>291336</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>124816</t>
+          <t>265049</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>346592</t>
+          <t>316027</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>516006</t>
+          <t>586576</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>303921</t>
+          <t>547019</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>602977</t>
+          <t>626012</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>310571</t>
+          <t>349575</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>281152</t>
+          <t>317328</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>344950</t>
+          <t>384636</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>492194</t>
+          <t>337366</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>352971</t>
+          <t>310635</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>722657</t>
+          <t>363876</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>802765</t>
+          <t>686941</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>669473</t>
+          <t>647888</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1116088</t>
+          <t>730323</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>136585</t>
+          <t>157338</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113642</t>
+          <t>131248</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163084</t>
+          <t>184205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>181103</t>
+          <t>182819</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88851</t>
+          <t>161053</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>259395</t>
+          <t>209098</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>317688</t>
+          <t>340156</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>208431</t>
+          <t>302175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>398340</t>
+          <t>378041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>703813</t>
+          <t>802152</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>703813</t>
+          <t>802152</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>703813</t>
+          <t>802152</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>932646</t>
+          <t>811521</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>932646</t>
+          <t>811521</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>932646</t>
+          <t>811521</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1636459</t>
+          <t>1613673</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1636459</t>
+          <t>1613673</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1636459</t>
+          <t>1613673</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>388275</t>
+          <t>401624</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>356676</t>
+          <t>368502</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>420673</t>
+          <t>435279</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>456073</t>
+          <t>493786</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>373975</t>
+          <t>464556</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>497149</t>
+          <t>523465</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>844348</t>
+          <t>895410</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>733267</t>
+          <t>853407</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>895299</t>
+          <t>937672</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,5%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>380561</t>
+          <t>420382</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>352289</t>
+          <t>383968</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>418962</t>
+          <t>453880</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>373108</t>
+          <t>409973</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>299728</t>
+          <t>380531</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>410518</t>
+          <t>438922</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>753669</t>
+          <t>830355</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>671240</t>
+          <t>787388</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>803798</t>
+          <t>872271</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>156020</t>
+          <t>165972</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>133038</t>
+          <t>142889</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>186150</t>
+          <t>193424</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>265751</t>
+          <t>215282</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>201315</t>
+          <t>193256</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>430351</t>
+          <t>238268</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>421771</t>
+          <t>381255</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>355405</t>
+          <t>348099</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>622690</t>
+          <t>417934</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>924856</t>
+          <t>987978</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>924856</t>
+          <t>987978</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>924856</t>
+          <t>987978</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2019788</t>
+          <t>2107020</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2019788</t>
+          <t>2107020</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2019788</t>
+          <t>2107020</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1066388</t>
+          <t>1147921</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>819866</t>
+          <t>1086313</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1169226</t>
+          <t>1208431</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1289430</t>
+          <t>1411713</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1033252</t>
+          <t>1357625</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1388564</t>
+          <t>1462032</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2355818</t>
+          <t>2559634</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2067202</t>
+          <t>2479688</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2531120</t>
+          <t>2639314</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1694895</t>
+          <t>1603414</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1545399</t>
+          <t>1542257</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2122918</t>
+          <t>1668941</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1634639</t>
+          <t>1598684</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1494700</t>
+          <t>1548051</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2023782</t>
+          <t>1656664</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3329534</t>
+          <t>3202098</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3069504</t>
+          <t>3120985</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3828642</t>
+          <t>3278085</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>45,18%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>691780</t>
+          <t>774504</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>510350</t>
+          <t>714044</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>766420</t>
+          <t>827131</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>733102</t>
+          <t>719773</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>616878</t>
+          <t>677799</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>920378</t>
+          <t>763996</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1424881</t>
+          <t>1494277</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1249143</t>
+          <t>1424424</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1631000</t>
+          <t>1566402</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3453062</t>
+          <t>3525839</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3453062</t>
+          <t>3525839</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3453062</t>
+          <t>3525839</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3657172</t>
+          <t>3730170</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3657172</t>
+          <t>3730170</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3657172</t>
+          <t>3730170</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7110233</t>
+          <t>7256009</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7110233</t>
+          <t>7256009</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7110233</t>
+          <t>7256009</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
